--- a/df_custos_placas.xlsx
+++ b/df_custos_placas.xlsx
@@ -58,7 +58,7 @@
     <t>NATUREZA</t>
   </si>
   <si>
-    <t>NIVELSUPERIOR</t>
+    <t>handle_nivel_superior</t>
   </si>
   <si>
     <t>desc_tipo_veic</t>
